--- a/記帳/申報/11508/11508期_兩家401申報整理包.xlsx
+++ b/記帳/申報/11508/11508期_兩家401申報整理包.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>來源:銷項媒體檔(妳上傳,已歸檔repo)</t>
+          <t>來源:銷項媒體檔(已歸檔repo)</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>留待下期</t>
+          <t>留待11509-10期</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>減:進項稅額(僅當期可扣抵)</t>
+          <t>減:進項稅額(當期可扣抵)</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -672,7 +672,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>如併入前期+待核+待確認進項</t>
+          <t>如併入前期+待確認進項</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -689,53 +689,37 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>1. 作廢3張(DU47478240/47478266/47478331)申報時列作廢;DU47478239經API查證為7/27開立予金屬工業中心,非廣廓,無誤。</t>
+          <t>1. 作廢3張(DU47478240/47478266/47478331);DU47478239為7/27開立予金屬工業中心(API查證),無誤。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2. 廣廓27,500已於115/9/11補開FW49988356,屬11509-10期銷項,不在本期。</t>
+          <t>2. 廣廓27,500已於115/9/11開立FW49988356,屬11509-10期。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3. 交際費(漢來禮券6張+餐費)進項稅§19不得扣抵,已另列。</t>
+          <t>3. 交際費進項稅§19不得扣抵。 4. iCHEF(DF13322559)補載統編發票後方可扣抵。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>4. iCHEF服務費(DF13322559)未確認載買方統編,取得正式發票後方可扣抵。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>5. 前期憑證(2~6月)若前期已申報請勿重複。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>6. 本表為試算,申報前請與記帳士或電子申報系統核對。</t>
+          <t>5. 前期憑證若已申報請勿重複。 6. 申報前請與記帳士或電子申報系統核對。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3549,7 +3533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3575,7 +3559,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>門市零售(POS/DQ字軌)7月</t>
+          <t>門市零售(POS/DQ)7月</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -3586,7 +3570,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>來源:日營業額報表(妳上傳);126,805÷1.05</t>
+          <t>日營業額報表;126,805÷1.05</t>
         </is>
       </c>
     </row>
@@ -3635,10 +3619,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>29157</v>
+        <v>214025</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1458</v>
+        <v>10701</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -3649,101 +3633,129 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>進項-待核日期</t>
+          <t>進項-前期憑證</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>205936</v>
+        <v>9989</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10296</v>
+        <v>499</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>核對票面日期後可扣抵</t>
+          <t>可扣抵(確認前期未重複)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>進項-不可扣抵</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3122</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>§19不得扣抵</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>進項-下期憑證</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>7957</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>398</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>留待11509-10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>三、應納(溢付)稅額試算</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>銷項稅額</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C15" s="3" t="n">
         <v>13634</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>減:進項稅額(僅當期可扣抵)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1458</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>應納稅額(負數=溢付留抵)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>12176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>如併入前期+待核+待確認進項</t>
+          <t>減:進項稅額(當期可扣抵)</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1880</v>
+        <v>10701</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>應納稅額(負數=溢付留抵)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2933</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>如併入前期+待確認進項</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>四、注意事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>1. 銷項以POS日營業額推算,請與綠界後台DQ字軌開立總額核對一致後申報。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2. 「待核日期」16張為9/5補拍照片,票面日期未逐張核對;屬7-8月者可扣抵(大額:輕車悠遊租金稅4,762、數字智慧1,714、農心1,667)。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3. 本表為試算,申報前請與記帳士或電子申報系統核對。</t>
+          <t>1. 16張補拍發票之號碼與票面日期已逐張核照片填入(115/9/11),當期12張/前期2張/下期2張。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2. 銷項請與綠界後台DQ字軌開立總額核對一致後申報。 3. 申報前請與記帳士或電子申報系統核對。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3871,10 +3883,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
+          <t>1150703</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>CV74151308</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>7-ELEVEN</t>
@@ -3901,22 +3917,26 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb8d5dcdb326;已核照片</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>1150707</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>DH80296395</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>金泉加油站</t>
@@ -3943,22 +3963,26 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb8e948f1592;油資;已核照片</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>1150601</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>BA93482190</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>中森加油站</t>
@@ -3985,22 +4009,26 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>前期憑證</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>前期未申報者可併入(勿重複)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>1150520</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BJ93882820</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>川本國際包裝</t>
@@ -4027,22 +4055,26 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>前期憑證</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>前期未申報者可併入(勿重複)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>1150708</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>CM57176357</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>IKEA台中</t>
@@ -4069,22 +4101,26 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb9374e57408;已核照片</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>1150817</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CA18808602</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>中橋美術</t>
@@ -4111,22 +4147,26 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb948f0b94fe;手寫買方統編;已核照片</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
+          <t>1150731</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>CA56123507</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>農心商行</t>
@@ -4153,22 +4193,26 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb951ef10326;冰棒一批;已核照片</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr"/>
+          <t>1150731</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>DT14638703</t>
+        </is>
+      </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
           <t>數字智慧</t>
@@ -4195,22 +4239,26 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb95d4f2b6c4;金銀花保養品;已核照片</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
+          <t>1150903</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EP55515992</t>
+        </is>
+      </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
           <t>IKEA新莊</t>
@@ -4237,22 +4285,26 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>下期憑證</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>屬11509-10期</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
+          <t>1150716</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>DG09229910</t>
+        </is>
+      </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
           <t>台灣國際開發停車</t>
@@ -4279,22 +4331,26 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb976e65e651;停車費;已核照片</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr"/>
+          <t>1150810</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DM57545084</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
           <t>天霖食品行</t>
@@ -4321,22 +4377,26 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb987af1e67f;已核照片</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr"/>
+          <t>1150804</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DH59002535</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>好市多Costco</t>
@@ -4363,22 +4423,26 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb98ae46f57f;已核照片</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr"/>
+          <t>1150901</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>FK58660047</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>好市多Costco</t>
@@ -4405,22 +4469,26 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>下期憑證</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>屬11509-10期</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr"/>
+          <t>1150818</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DD88022938</t>
+        </is>
+      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>福容大飯店</t>
@@ -4447,22 +4515,26 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>不可扣抵</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>§19交際應酬不得扣抵</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
+          <t>1150810</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DM05253424</t>
+        </is>
+      </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>川本國際包裝</t>
@@ -4489,22 +4561,26 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb9a11e6dec7;咖啡包材;已核照片</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>1150905</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr"/>
+          <t>1150827</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>DQ33588277</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>輕車悠遊股份有限公司</t>
@@ -4531,12 +4607,12 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>待核日期</t>
+          <t>當期可扣抵</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>收件9/5票面日期未核;核為7-8月即可扣抵</t>
+          <t>訊息1a06fb9a5ab63d1f;場地租金;已核照片</t>
         </is>
       </c>
     </row>
